--- a/Trắc nghiệm bài kiểm tra đánh giá đầu vào/da-sql-medium.xlsx
+++ b/Trắc nghiệm bài kiểm tra đánh giá đầu vào/da-sql-medium.xlsx
@@ -460,19 +460,19 @@
         <v>WHERE lọc các bản ghi nguồn (rows) trước khi tính toán gom nhóm. HAVING dùng để lọc các nhóm (groups) thỏa mãn điều kiện trên các hàm aggregate.</v>
       </c>
       <c r="F2" t="str">
+        <v>WHERE chỉ dùng cho kiểu dữ liệu số; HAVING chỉ dùng cho kiểu dữ liệu chuỗi ký tự</v>
+      </c>
+      <c r="G2" t="str">
+        <v>WHERE bắt buộc phải có trong mọi truy vấn; HAVING chỉ dùng khi thực hiện phép nối LEFT JOIN</v>
+      </c>
+      <c r="H2" t="str">
         <v>WHERE lọc dữ liệu trước khi gom nhóm (GROUP BY); HAVING lọc kết quả sau khi đã gom nhóm và tính toán hàm aggregate</v>
       </c>
-      <c r="G2" t="str">
-        <v>WHERE chỉ dùng cho kiểu dữ liệu số; HAVING chỉ dùng cho kiểu dữ liệu chuỗi ký tự</v>
-      </c>
-      <c r="H2" t="str">
+      <c r="I2" t="str">
         <v>WHERE đứng sau mệnh đề GROUP BY; HAVING đứng trước mệnh đề GROUP BY</v>
       </c>
-      <c r="I2" t="str">
-        <v>WHERE bắt buộc phải có trong mọi truy vấn; HAVING chỉ dùng khi thực hiện phép nối LEFT JOIN</v>
-      </c>
       <c r="J2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -492,19 +492,19 @@
         <v>Hàm `ROW_NUMBER() OVER` là Window Function. `PARTITION BY department_id` chia nhân viên thành các nhóm theo phòng ban, và `ORDER BY salary DESC` đánh số thứ tự từ 1 (lương cao nhất) đến hết trong nhóm đó.</v>
       </c>
       <c r="F3" t="str">
-        <v>Đánh số thứ tự tăng dần từ 1 cho nhân viên trong từng phòng ban theo mức lương giảm dần — hàm phân tích cửa sổ (Window Function)</v>
+        <v>Sắp xếp toàn bộ bảng nhân viên theo thứ tự phòng ban tăng dần và lương giảm dần — sắp xếp bảng</v>
       </c>
       <c r="G3" t="str">
         <v>Tính tổng lương của nhân viên trong từng phòng ban một cách tự động — hàm gom nhóm</v>
       </c>
       <c r="H3" t="str">
+        <v>Đánh số thứ tự tăng dần từ 1 cho nhân viên trong từng phòng ban theo mức lương giảm dần — hàm phân tích cửa sổ (Window Function)</v>
+      </c>
+      <c r="I3" t="str">
         <v>Xóa bỏ các nhân viên có lương trùng nhau trong cùng một phòng ban — lọc dữ liệu</v>
       </c>
-      <c r="I3" t="str">
-        <v>Sắp xếp toàn bộ bảng nhân viên theo thứ tự phòng ban tăng dần và lương giảm dần — sắp xếp bảng</v>
-      </c>
       <c r="J3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -530,10 +530,10 @@
         <v>Chuyển đổi kiểu dữ liệu của cột column_name thành kiểu số nguyên (Integer)</v>
       </c>
       <c r="H4" t="str">
+        <v>Tự động cộng thêm 0 vào tất cả các giá trị số trong cột column_name</v>
+      </c>
+      <c r="I4" t="str">
         <v>Đếm số lượng giá trị NULL xuất hiện trong cột column_name của bảng dữ liệu</v>
-      </c>
-      <c r="I4" t="str">
-        <v>Tự động cộng thêm 0 vào tất cả các giá trị số trong cột column_name</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -588,19 +588,19 @@
         <v>Hàm aggregate `COUNT(OrderID)` không được phép đặt trong WHERE. Điều kiện lọc số đơn hàng của từng nhóm khách hàng phải được đặt ở mệnh đề HAVING sau GROUP BY.</v>
       </c>
       <c r="F6" t="str">
+        <v>SELECT CustomerID, SUM(OrderID) FROM Orders GROUP BY CustomerID HAVING SUM(OrderID) &gt; 5;</v>
+      </c>
+      <c r="G6" t="str">
         <v>SELECT CustomerID, COUNT(OrderID) FROM Orders GROUP BY CustomerID HAVING COUNT(OrderID) &gt; 5;</v>
       </c>
-      <c r="G6" t="str">
+      <c r="H6" t="str">
         <v>SELECT CustomerID, COUNT(OrderID) FROM Orders WHERE COUNT(OrderID) &gt; 5 GROUP BY CustomerID;</v>
-      </c>
-      <c r="H6" t="str">
-        <v>SELECT CustomerID, SUM(OrderID) FROM Orders GROUP BY CustomerID HAVING SUM(OrderID) &gt; 5;</v>
       </c>
       <c r="I6" t="str">
         <v>SELECT CustomerID, COUNT(OrderID) FROM Orders GROUP BY CustomerID WHERE COUNT(OrderID) &gt; 5;</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -620,19 +620,19 @@
         <v>UNION lọc trùng lặp (duplication removal), do đó tốn tài nguyên sắp xếp/lọc hơn. UNION ALL chỉ ghép nối cơ học tập kết quả nên nhanh hơn.</v>
       </c>
       <c r="F7" t="str">
+        <v>UNION chỉ chạy được trên kiểu dữ liệu số; UNION ALL chạy được trên mọi kiểu dữ liệu</v>
+      </c>
+      <c r="G7" t="str">
+        <v>UNION gộp bảng theo chiều ngang (thêm cột); UNION ALL gộp bảng theo chiều dọc (thêm dòng)</v>
+      </c>
+      <c r="H7" t="str">
         <v>UNION loại bỏ các dòng kết quả trùng lặp; UNION ALL giữ lại toàn bộ các dòng kết quả kể cả dòng trùng lặp</v>
       </c>
-      <c r="G7" t="str">
-        <v>UNION chỉ chạy được trên kiểu dữ liệu số; UNION ALL chạy được trên mọi kiểu dữ liệu</v>
-      </c>
-      <c r="H7" t="str">
+      <c r="I7" t="str">
         <v>UNION ALL thực hiện nhanh hơn UNION vì nó không cần thực hiện thêm bước kiểm tra và lọc trùng lặp — hiệu năng tối ưu hơn</v>
       </c>
-      <c r="I7" t="str">
-        <v>UNION gộp bảng theo chiều ngang (thêm cột); UNION ALL gộp bảng theo chiều dọc (thêm dòng)</v>
-      </c>
       <c r="J7">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -652,19 +652,19 @@
         <v>CTE định nghĩa các bảng tạm ảo trong phạm vi câu lệnh, giúp phân rã các truy vấn lồng nhau phức tạp thành các khối mã tuần tự, cải thiện độ trực quan.</v>
       </c>
       <c r="F8" t="str">
+        <v>Khi cần kết nối hai database nằm ở hai máy chủ vật lý khác nhau trên mạng</v>
+      </c>
+      <c r="G8" t="str">
         <v>Khi truy vấn phức tạp, lồng nhiều cấp hoặc cần tái sử dụng cùng một tập kết quả trung gian nhiều lần — giúp code rõ ràng, dễ đọc và bảo trì</v>
-      </c>
-      <c r="G8" t="str">
-        <v>Khi cơ sở dữ liệu yêu cầu bắt buộc phải chạy song song nhiều câu lệnh INSERT</v>
       </c>
       <c r="H8" t="str">
         <v>Khi cần tăng tốc độ thực thi của câu lệnh SELECT lên gấp nhiều lần mà không dùng Index</v>
       </c>
       <c r="I8" t="str">
-        <v>Khi cần kết nối hai database nằm ở hai máy chủ vật lý khác nhau trên mạng</v>
+        <v>Khi cơ sở dữ liệu yêu cầu bắt buộc phải chạy song song nhiều câu lệnh INSERT</v>
       </c>
       <c r="J8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -684,10 +684,10 @@
         <v>Index tạo ra một cấu trúc cây tìm kiếm (thường là B-Tree) giúp công cụ tìm dữ liệu nhanh hơn mà không cần quét toàn bộ bảng (Table Scan). Tuy nhiên, mỗi lần ghi dữ liệu, DB phải cập nhật lại cây Index nên làm ghi chậm hơn.</v>
       </c>
       <c r="F9" t="str">
+        <v>Đảm bảo dữ liệu trong cột đó không bao giờ bị ghi đè hoặc chỉnh sửa bởi người dùng</v>
+      </c>
+      <c r="G9" t="str">
         <v>Tăng tốc độ tìm kiếm và truy vấn dữ liệu (SELECT) trên cột đó; làm chậm tốc độ ghi dữ liệu (INSERT/UPDATE/DELETE)</v>
-      </c>
-      <c r="G9" t="str">
-        <v>Đảm bảo dữ liệu trong cột đó không bao giờ bị ghi đè hoặc chỉnh sửa bởi người dùng</v>
       </c>
       <c r="H9" t="str">
         <v>Tự động định dạng lại font chữ và kiểu hiển thị của dữ liệu trong bảng kết quả</v>
@@ -696,7 +696,7 @@
         <v>Tạo ra một bảng sao lưu dự phòng tự động của cột dữ liệu đó để tránh mất mát</v>
       </c>
       <c r="J9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -716,19 +716,19 @@
         <v>Ví dụ với mức lương: 100, 100, 80. RANK() sẽ đánh số: 1, 1, 3 (nhảy qua số 2). DENSE_RANK() đánh số: 1, 1, 2 (đảm bảo số thứ tự liên tục).</v>
       </c>
       <c r="F10" t="str">
+        <v>RANK() trả về tổng số dòng; DENSE_RANK() trả về số dòng duy nhất</v>
+      </c>
+      <c r="G10" t="str">
+        <v>RANK() sắp xếp tăng dần; DENSE_RANK() sắp xếp giảm dần một cách tự động</v>
+      </c>
+      <c r="H10" t="str">
+        <v>RANK() chỉ chạy trên các cột số nguyên; DENSE_RANK() chạy trên mọi kiểu dữ liệu số</v>
+      </c>
+      <c r="I10" t="str">
         <v>RANK() bỏ qua các số thứ tự tiếp theo (tạo khoảng nhảy); DENSE_RANK() đánh số liên tục không tạo khoảng nhảy</v>
       </c>
-      <c r="G10" t="str">
-        <v>RANK() chỉ chạy trên các cột số nguyên; DENSE_RANK() chạy trên mọi kiểu dữ liệu số</v>
-      </c>
-      <c r="H10" t="str">
-        <v>RANK() sắp xếp tăng dần; DENSE_RANK() sắp xếp giảm dần một cách tự động</v>
-      </c>
-      <c r="I10" t="str">
-        <v>RANK() trả về tổng số dòng; DENSE_RANK() trả về số dòng duy nhất</v>
-      </c>
       <c r="J10">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -748,7 +748,7 @@
         <v>Dạng chuẩn 3 (3NF) loại bỏ các phụ thuộc bắc cầu. Nghĩa là không có cột phi khóa nào được xác định thông qua một cột phi khóa khác.</v>
       </c>
       <c r="F11" t="str">
-        <v>Bảng phải đạt chuẩn 2 (2NF) và không tồn tại phụ thuộc bắc cầu (transitive dependency) giữa các cột phi khóa chính</v>
+        <v>Bảng không được chứa quá 10 cột dữ liệu và không được có dòng nào chứa giá trị NULL</v>
       </c>
       <c r="G11" t="str">
         <v>Bảng phải chứa tối thiểu một cột khóa chính và một cột khóa ngoại liên kết bảng khác</v>
@@ -757,10 +757,10 @@
         <v>Tất cả các cột dữ liệu trong bảng bắt buộc phải được khai báo kiểu dữ liệu văn bản</v>
       </c>
       <c r="I11" t="str">
-        <v>Bảng không được chứa quá 10 cột dữ liệu và không được có dòng nào chứa giá trị NULL</v>
+        <v>Bảng phải đạt chuẩn 2 (2NF) và không tồn tại phụ thuộc bắc cầu (transitive dependency) giữa các cột phi khóa chính</v>
       </c>
       <c r="J11">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
